--- a/appointment_forms/038_court_hearing_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/038_court_hearing_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>court_hearing_appointment_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter any additional information</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>court_date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Court Date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter the court date</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>court_time</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Court Time</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter the court time</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>User Name</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter your name</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>user_email</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>User Email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter your email</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>user_phone</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>User Phone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +687,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>user_address</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>User Address</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter your address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>case_number</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Case Number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the case number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +741,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>court_number</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Court Number</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter the court number</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +768,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hearing_type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Hearing Type</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select your hearing type</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +795,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>preferred_dates</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Preferred Dates</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select your preferred dates</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +822,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>available_dates</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Available Dates</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select your available dates</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,13 +849,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>available_time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Available Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select your available time</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +876,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>preferred_time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Preferred Time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select your preferred time</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,10 +903,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter any comments</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -870,10 +930,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter the assigned tool</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -893,10 +957,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Form IDs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter the form IDs</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -916,13 +984,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter the category</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -939,13 +1011,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Enter the description</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -962,13 +1038,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Enter the title</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -985,13 +1065,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>category_title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Category Title</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Enter the category title</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1008,13 +1092,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>description_title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Description Title</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Enter the description title</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1114,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_title</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Assigned Tool Title</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Enter the assigned tool</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,15 +1141,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>category_title</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>category_title</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Assigned Tool 2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Enter the assigned tool</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
@@ -1072,15 +1168,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>category_title_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Category Title 2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Enter the category title</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
@@ -1102,7 +1202,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1131,12 +1231,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1248,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1265,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1282,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1299,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1316,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1333,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1350,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1367,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1384,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
